--- a/output/pdf_financials_xlsx/GURU.xlsx
+++ b/output/pdf_financials_xlsx/GURU.xlsx
@@ -12136,10 +12136,10 @@
         </is>
       </c>
       <c r="E149" s="5" t="n">
-        <v>0.679725</v>
+        <v>-0.679725</v>
       </c>
       <c r="F149" s="5" t="n">
-        <v>0.269157</v>
+        <v>-0.269157</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         </is>
       </c>
       <c r="E166" s="5" t="n">
-        <v>0.679725</v>
+        <v>-0.679725</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/GURU.xlsx
+++ b/output/pdf_financials_xlsx/GURU.xlsx
@@ -1480,10 +1480,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.355402</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.090777</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>66.953636</v>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.355402</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.090777</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>66.953636</v>
@@ -1872,10 +1872,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.355402</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.090777</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.7861089999999999</v>
@@ -8059,7 +8059,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">

--- a/output/pdf_financials_xlsx/GURU.xlsx
+++ b/output/pdf_financials_xlsx/GURU.xlsx
@@ -510,15 +510,11 @@
       <c r="C4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D4" s="3" t="n">
+        <v>30.190919</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>29.080953</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>29.28832</v>
@@ -542,15 +538,11 @@
       <c r="C5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D5" s="3" t="n">
+        <v>12.307947</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>13.387834</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>13.853084</v>
@@ -574,15 +566,11 @@
       <c r="C6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D6" s="3" t="n">
+        <v>17.882972</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>15.693119</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>15.435236</v>
@@ -606,15 +594,11 @@
       <c r="C7" s="3" t="n">
         <v>0.06542199999999999</v>
       </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D7" s="3" t="n">
+        <v>27.800985</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>34.115532</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>29.149295</v>
@@ -638,15 +622,11 @@
       <c r="C8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0</v>
@@ -670,15 +650,11 @@
       <c r="C9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
@@ -702,15 +678,11 @@
       <c r="C10" s="3" t="n">
         <v>0.06542199999999999</v>
       </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D10" s="3" t="n">
+        <v>27.800985</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>34.115532</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>29.149295</v>
@@ -734,15 +706,11 @@
       <c r="C11" s="3" t="n">
         <v>-0.06542199999999999</v>
       </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D11" s="3" t="n">
+        <v>-9.918013</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>-18.422413</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>-13.714059</v>
@@ -766,15 +734,11 @@
       <c r="C12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -798,15 +762,11 @@
       <c r="C13" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>-0</v>
@@ -830,15 +790,11 @@
       <c r="C14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>0</v>
@@ -862,15 +818,11 @@
       <c r="C15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>0</v>
@@ -894,15 +846,11 @@
       <c r="C16" s="3" t="n">
         <v>-0.679725</v>
       </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D16" s="3" t="n">
+        <v>-10.075391</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-17.54466</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>-11.956105</v>
@@ -926,15 +874,11 @@
       <c r="C17" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="D17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D17" s="3" t="n">
+        <v>0.231218</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>-0.020317</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-0.006208</v>
@@ -1042,15 +986,11 @@
       <c r="C20" s="3" t="n">
         <v>-0.679725</v>
       </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D20" s="3" t="n">
+        <v>-9.844173</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>-17.564977</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>-11.962313</v>
@@ -1074,15 +1014,11 @@
       <c r="C21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>0</v>
@@ -1106,15 +1042,11 @@
       <c r="C22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>0</v>
@@ -1138,15 +1070,11 @@
       <c r="C23" s="3" t="n">
         <v>-0.679725</v>
       </c>
-      <c r="D23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D23" s="3" t="n">
+        <v>-9.844173</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>-17.564977</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>-11.962313</v>
@@ -1174,15 +1102,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D24" s="3" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>-0.54</v>
       </c>
       <c r="F24" s="3" t="n">
         <v>-0.38</v>
@@ -1210,15 +1134,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D25" s="3" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>-0.54</v>
       </c>
       <c r="F25" s="3" t="n">
         <v>-0.38</v>
@@ -1246,15 +1166,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D26" s="3" t="n">
+        <v>29.830827</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>32.527735</v>
       </c>
       <c r="F26" s="3" t="n">
         <v>31.479771</v>
@@ -1278,15 +1194,11 @@
       <c r="C27" s="3" t="n">
         <v>-0.679725</v>
       </c>
-      <c r="D27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D27" s="3" t="n">
+        <v>-10.075391</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>-17.54466</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-11.956105</v>
@@ -1310,15 +1222,11 @@
       <c r="C28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D28" s="3" t="n">
+        <v>0.516948</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>0.877258</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>1.179367</v>
@@ -1342,15 +1250,11 @@
       <c r="C29" s="3" t="n">
         <v>-0.679725</v>
       </c>
-      <c r="D29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D29" s="3" t="n">
+        <v>-9.558443</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>-16.667402</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-10.776738</v>
@@ -1378,15 +1282,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D30" s="3" t="n">
+        <v>-31.65999352321802</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>-57.31380948898064</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>-36.79534367283613</v>
@@ -1410,15 +1310,11 @@
       <c r="C31" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="D31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D31" s="3" t="n">
+        <v>-2.294878680142537</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>-0.1158016171302265</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-0.05192326430723049</v>
@@ -1446,15 +1342,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D32" s="3" t="n">
+        <v>-32.60640393225525</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>-60.40027986703187</v>
       </c>
       <c r="F32" s="3" t="n">
         <v>-40.84328838253611</v>
@@ -2446,10 +2338,10 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.076764</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.07736700000000001</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>0</v>
@@ -2477,7 +2369,7 @@
         <v>0.08121399999999999</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0.085746</v>
+        <v>0.163113</v>
       </c>
       <c r="D68" s="3" t="n">
         <v>10.265265</v>
@@ -3374,15 +3266,11 @@
       <c r="C99" s="3" t="n">
         <v>-0.269157</v>
       </c>
-      <c r="D99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D99" s="3" t="n">
+        <v>-9.844173</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>-17.564977</v>
       </c>
       <c r="F99" s="3" t="n">
         <v>-11.962313</v>
@@ -3406,15 +3294,11 @@
       <c r="C100" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D100" s="3" t="n">
+        <v>0.516948</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>0.877258</v>
       </c>
       <c r="F100" s="3" t="n">
         <v>1.179367</v>
@@ -3438,15 +3322,11 @@
       <c r="C101" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F101" s="3" t="n">
         <v>0</v>
@@ -3470,15 +3350,11 @@
       <c r="C102" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F102" s="3" t="n">
         <v>0</v>
@@ -3502,15 +3378,11 @@
       <c r="C103" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F103" s="3" t="n">
         <v>0</v>
@@ -3534,15 +3406,11 @@
       <c r="C104" s="3" t="n">
         <v>0.004532</v>
       </c>
-      <c r="D104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F104" s="3" t="n">
         <v>0</v>
@@ -3566,15 +3434,11 @@
       <c r="C105" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F105" s="3" t="n">
         <v>0</v>
@@ -3598,24 +3462,20 @@
       <c r="C106" s="3" t="n">
         <v>-0.264625</v>
       </c>
-      <c r="D106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D106" s="3" t="n">
+        <v>-1.034781</v>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>-1.538268</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0</v>
+        <v>2.566806</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0</v>
+        <v>-0.013493</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0</v>
+        <v>3.561389</v>
       </c>
     </row>
     <row r="107">
@@ -3630,15 +3490,11 @@
       <c r="C107" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D107" s="3" t="n">
+        <v>0.455322</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>0.334419</v>
       </c>
       <c r="F107" s="3" t="n">
         <v>0.6367620000000001</v>
@@ -3662,15 +3518,11 @@
       <c r="C108" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F108" s="3" t="n">
         <v>0</v>
@@ -3694,15 +3546,11 @@
       <c r="C109" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F109" s="3" t="n">
         <v>0</v>
@@ -3726,15 +3574,11 @@
       <c r="C110" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F110" s="3" t="n">
         <v>0</v>
@@ -3758,15 +3602,11 @@
       <c r="C111" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F111" s="3" t="n">
         <v>0</v>
@@ -3790,15 +3630,11 @@
       <c r="C112" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F112" s="3" t="n">
         <v>0</v>
@@ -3822,15 +3658,11 @@
       <c r="C113" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F113" s="3" t="n">
         <v>0</v>
@@ -3854,15 +3686,11 @@
       <c r="C114" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F114" s="3" t="n">
         <v>0</v>
@@ -3886,15 +3714,11 @@
       <c r="C115" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F115" s="3" t="n">
         <v>0</v>
@@ -3918,15 +3742,11 @@
       <c r="C116" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F116" s="3" t="n">
         <v>0</v>
@@ -3950,15 +3770,11 @@
       <c r="C117" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F117" s="3" t="n">
         <v>0</v>
@@ -3982,15 +3798,11 @@
       <c r="C118" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F118" s="3" t="n">
         <v>0</v>
@@ -4056,15 +3868,11 @@
       <c r="C120" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F120" s="3" t="n">
         <v>0</v>
@@ -4088,15 +3896,11 @@
       <c r="C121" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F121" s="3" t="n">
         <v>0</v>
@@ -4120,15 +3924,11 @@
       <c r="C122" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F122" s="3" t="n">
         <v>0</v>
@@ -4152,15 +3952,11 @@
       <c r="C123" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F123" s="3" t="n">
         <v>0</v>
@@ -4184,15 +3980,11 @@
       <c r="C124" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D124" s="3" t="n">
+        <v>-0.275</v>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F124" s="3" t="n">
         <v>0</v>
@@ -4216,15 +4008,11 @@
       <c r="C125" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D125" s="3" t="n">
+        <v>-0.275</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F125" s="3" t="n">
         <v>0</v>
@@ -4248,15 +4036,11 @@
       <c r="C126" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F126" s="3" t="n">
         <v>0</v>
@@ -4322,24 +4106,20 @@
       <c r="C128" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D128" s="3" t="n">
+        <v>-2.938418</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>-0.076304</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>0</v>
+        <v>-0.059372</v>
       </c>
       <c r="G128" s="3" t="n">
-        <v>0</v>
+        <v>-0.045156</v>
       </c>
       <c r="H128" s="3" t="n">
-        <v>0</v>
+        <v>-0.036473</v>
       </c>
     </row>
     <row r="129">
@@ -4396,15 +4176,11 @@
       <c r="C130" s="3" t="n">
         <v>0.355402</v>
       </c>
-      <c r="D130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D130" s="3" t="n">
+        <v>30.418296</v>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>66.953636</v>
       </c>
       <c r="F130" s="3" t="n">
         <v>25.491029</v>
@@ -4428,15 +4204,11 @@
       <c r="C131" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F131" s="3" t="n">
         <v>0</v>
@@ -4460,15 +4232,11 @@
       <c r="C132" s="3" t="n">
         <v>-0.264625</v>
       </c>
-      <c r="D132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D132" s="3" t="n">
+        <v>36.53534</v>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>-41.462607</v>
       </c>
       <c r="F132" s="3" t="n">
         <v>-9.665212</v>
@@ -4492,15 +4260,11 @@
       <c r="C133" s="3" t="n">
         <v>0.090777</v>
       </c>
-      <c r="D133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D133" s="3" t="n">
+        <v>66.953636</v>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>25.491029</v>
       </c>
       <c r="F133" s="3" t="n">
         <v>15.825817</v>
@@ -4524,15 +4288,11 @@
       <c r="C134" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F134" s="3" t="n">
         <v>0</v>
@@ -4597,7 +4357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K167"/>
+  <dimension ref="A1:K209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5489,7 +5249,11 @@
           <t>Lease liabilities (note 13)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -7021,7 +6785,11 @@
           <t>Lease liabilities (note 13)</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -7853,7 +7621,11 @@
           <t>Lease liabilities (note 14)</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -8443,20 +8215,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G75" s="5" t="n">
+        <v>-9.844173</v>
+      </c>
+      <c r="H75" s="5" t="n">
+        <v>-17.564977</v>
+      </c>
+      <c r="I75" s="5" t="n">
+        <v>-11.962313</v>
       </c>
       <c r="J75" s="5" t="n">
         <v>-9.410052</v>
@@ -8785,7 +8551,11 @@
           <t>Net change in non-cash operating working capital (note 20)</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -8845,15 +8615,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G83" s="5" t="n">
+        <v>-10.156282</v>
+      </c>
+      <c r="H83" s="5" t="n">
+        <v>-18.839523</v>
       </c>
       <c r="I83" s="5" t="n">
         <v>-9.318984</v>
@@ -8897,10 +8663,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H84" s="5" t="n">
+        <v>-0.5953270000000001</v>
       </c>
       <c r="I84" s="5" t="n">
         <v>-4.017037</v>
@@ -8983,7 +8747,11 @@
           <t>Interest and financing fees paid</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -8994,15 +8762,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G86" s="5" t="n">
+        <v>-0.113342</v>
+      </c>
+      <c r="H86" s="5" t="n">
+        <v>-0.076304</v>
       </c>
       <c r="I86" s="5" t="n">
         <v>-0.059372</v>
@@ -9088,15 +8852,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G88" s="5" t="n">
+        <v>47.816552</v>
+      </c>
+      <c r="H88" s="5" t="n">
+        <v>-1.000488</v>
       </c>
       <c r="I88" s="5" t="n">
         <v>-4.476491</v>
@@ -9184,15 +8944,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G90" s="5" t="n">
+        <v>-1.158316</v>
+      </c>
+      <c r="H90" s="5" t="n">
+        <v>-0.56633</v>
       </c>
       <c r="I90" s="5" t="n">
         <v>-0.07788100000000001</v>
@@ -9236,10 +8992,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H91" s="5" t="n">
+        <v>0.398919</v>
       </c>
       <c r="I91" s="5" t="n">
         <v>1.29021</v>
@@ -9278,15 +9032,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G92" s="5" t="n">
+        <v>-1.103363</v>
+      </c>
+      <c r="H92" s="5" t="n">
+        <v>-21.646682</v>
       </c>
       <c r="I92" s="5" t="n">
         <v>4.113329</v>
@@ -9325,15 +9075,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G93" s="5" t="n">
+        <v>-0.021567</v>
+      </c>
+      <c r="H93" s="5" t="n">
+        <v>0.024086</v>
       </c>
       <c r="I93" s="5" t="n">
         <v>0.016934</v>
@@ -9376,15 +9122,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G94" s="5" t="n">
+        <v>30.418296</v>
+      </c>
+      <c r="H94" s="5" t="n">
+        <v>66.953636</v>
       </c>
       <c r="I94" s="5" t="n">
         <v>25.491029</v>
@@ -9678,15 +9420,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G100" s="5" t="n">
+        <v>0.516948</v>
+      </c>
+      <c r="H100" s="5" t="n">
+        <v>0.877258</v>
       </c>
       <c r="I100" s="5" t="n">
         <v>1.179367</v>
@@ -9732,10 +9470,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H101" s="5" t="n">
+        <v>0.020317</v>
       </c>
       <c r="I101" s="5" t="n">
         <v>0.006208</v>
@@ -9776,15 +9512,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G102" s="5" t="n">
+        <v>-0.028599</v>
+      </c>
+      <c r="H102" s="5" t="n">
+        <v>-0.952203</v>
       </c>
       <c r="I102" s="5" t="n">
         <v>-1.757954</v>
@@ -9969,7 +9701,11 @@
           <t>Net change in non-cash operating working capital (note 22)</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -9980,15 +9716,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G106" s="5" t="n">
+        <v>-1.034781</v>
+      </c>
+      <c r="H106" s="5" t="n">
+        <v>-1.538268</v>
       </c>
       <c r="I106" s="5" t="n">
         <v>2.566806</v>
@@ -10029,15 +9761,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G107" s="5" t="n">
+        <v>1.782218</v>
+      </c>
+      <c r="H107" s="5" t="n">
+        <v>0.061843</v>
       </c>
       <c r="I107" s="5" t="n">
         <v>0.003989</v>
@@ -10134,10 +9862,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H109" s="5" t="n">
+        <v>-0.679271</v>
       </c>
       <c r="I109" s="5" t="n">
         <v>0.001</v>
@@ -10212,35 +9938,37 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Incorporation</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>December 31, 2019 December</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
-      <c r="E111" s="5" t="n">
-        <v>0.002018</v>
-      </c>
-      <c r="F111" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Stock-based compensation expense</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G111" s="5" t="n">
+        <v>0.455322</v>
+      </c>
+      <c r="H111" s="5" t="n">
+        <v>0.334419</v>
+      </c>
+      <c r="I111" s="5" t="n">
+        <v>0.6367620000000001</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -10261,34 +9989,32 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Net loss for the period $</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E112" s="5" t="n">
-        <v>-0.679725</v>
-      </c>
-      <c r="F112" s="5" t="n">
-        <v>-0.269157</v>
+          <t>Additions to other assets</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H112" s="5" t="n">
+        <v>-0.016069</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -10314,21 +10040,23 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Item not affecting cash</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Stock based compensation</t>
+          <t>Net change in non-cash operating working capital (note 21)</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
-      <c r="E113" s="5" t="n">
-        <v>0.1323</v>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10340,15 +10068,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H113" s="5" t="n">
+        <v>-1.538268</v>
+      </c>
+      <c r="I113" s="5" t="n">
+        <v>2.566806</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -10369,39 +10093,33 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital</t>
+          <t>Financing</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E114" s="5" t="n">
-        <v>0.08121399999999999</v>
-      </c>
-      <c r="F114" s="5" t="n">
-        <v>0.004532</v>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Payment of lease obligations</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>-0.300432</v>
+      </c>
+      <c r="H114" s="5" t="n">
+        <v>-0.3907</v>
+      </c>
+      <c r="I114" s="5" t="n">
+        <v>-0.404071</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -10422,39 +10140,35 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital</t>
+          <t>Investing</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital total</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>ChangeInWorkingCapital</t>
-        </is>
-      </c>
-      <c r="E115" s="5" t="n">
-        <v>-0.466211</v>
-      </c>
-      <c r="F115" s="5" t="n">
-        <v>-0.264625</v>
+          <t>Decrease (increase) in short-term investments</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H115" s="5" t="n">
+        <v>-20.8</v>
+      </c>
+      <c r="I115" s="5" t="n">
+        <v>2.8</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -10475,17 +10189,19 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Net proceeds on issuance of common stock</t>
+          <t>Refund of lease deposit</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
-      <c r="E116" s="5" t="n">
-        <v>0.821613</v>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10502,10 +10218,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I116" s="5" t="n">
+        <v>0.001</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -10526,12 +10240,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Net change in cash during the period $</t>
+          <t>Decrease in cash and cash equivalents</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -10539,26 +10253,26 @@
           <t>ChangesInCash</t>
         </is>
       </c>
-      <c r="E117" s="5" t="n">
-        <v>0.355402</v>
-      </c>
-      <c r="F117" s="5" t="n">
-        <v>-0.264625</v>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H117" s="5" t="n">
+        <v>-41.462607</v>
+      </c>
+      <c r="I117" s="5" t="n">
+        <v>-9.665212</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -10579,17 +10293,17 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Cash, beginning of period</t>
+          <t>Cash and cash equivalents, end of year $</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -10597,23 +10311,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F118" s="5" t="n">
-        <v>0.355402</v>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G118" s="5" t="n">
+        <v>66.953636</v>
+      </c>
+      <c r="H118" s="5" t="n">
+        <v>25.491029</v>
+      </c>
+      <c r="I118" s="5" t="n">
+        <v>15.825817</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -10634,39 +10344,35 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>International Accounting Standards Board ("IASB").</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Cash, end of period $</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
-      <c r="E119" s="5" t="n">
-        <v>0.355402</v>
-      </c>
-      <c r="F119" s="5" t="n">
-        <v>0.090777</v>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H119" s="5" t="n">
+        <v>0.002024</v>
+      </c>
+      <c r="I119" s="5" t="n">
+        <v>2.4e-05</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -10687,19 +10393,15 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Cash, beginning of period $</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Income tax expense (recovery)</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>
@@ -10710,15 +10412,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G120" s="5" t="n">
+        <v>-0.231218</v>
+      </c>
+      <c r="H120" s="5" t="n">
+        <v>0.020317</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -10739,20 +10437,20 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Adjustments for</t>
+        </is>
+      </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Net revenue (note 15) $</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
+          <t>Derecognition of right-of-use asset and lease liabilities</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>
@@ -10763,43 +10461,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G121" s="5" t="n">
+        <v>-0.000329</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I121" s="5" t="n">
-        <v>29.28832</v>
-      </c>
-      <c r="J121" s="5" t="n">
-        <v>30.242255</v>
-      </c>
-      <c r="K121" s="5" t="n">
-        <v>34.74792</v>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Adjustments for</t>
+        </is>
+      </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Cost of goods sold</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>CostOfRevenue</t>
-        </is>
-      </c>
+          <t>Additions to other assets (note 11)</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
           <t>-</t>
@@ -10810,43 +10512,45 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I122" s="5" t="n">
-        <v>13.853084</v>
-      </c>
-      <c r="J122" s="5" t="n">
-        <v>13.506585</v>
-      </c>
-      <c r="K122" s="5" t="n">
-        <v>12.268083</v>
+      <c r="G122" s="5" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="H122" s="5" t="n">
+        <v>-0.016069</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Adjustments for</t>
+        </is>
+      </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Gross profit</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>GrossProfit</t>
-        </is>
-      </c>
+          <t>Loss on disposition of fixed assets</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
@@ -10857,43 +10561,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G123" s="5" t="n">
+        <v>0.023362</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I123" s="5" t="n">
-        <v>15.435236</v>
-      </c>
-      <c r="J123" s="5" t="n">
-        <v>16.73567</v>
-      </c>
-      <c r="K123" s="5" t="n">
-        <v>22.479837</v>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Adjustments for</t>
+        </is>
+      </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Selling, general and administration expenses (note 16)</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Income tax received</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -10904,39 +10612,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G124" s="5" t="n">
+        <v>0.012186</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I124" s="5" t="n">
-        <v>29.149295</v>
-      </c>
-      <c r="J124" s="5" t="n">
-        <v>27.301846</v>
-      </c>
-      <c r="K124" s="5" t="n">
-        <v>24.572052</v>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Financing</t>
+        </is>
+      </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Restructuring expenses</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr"/>
+          <t>Share issuance from public offering and private placement</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>
@@ -10947,10 +10667,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G125" s="5" t="n">
+        <v>49.561502</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -10962,8 +10680,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J125" s="5" t="n">
-        <v>0.194252</v>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
@@ -10974,16 +10694,24 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Financing</t>
+        </is>
+      </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Net financial income (note 17)</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr"/>
+          <t>Share issuance costs</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>-</t>
@@ -10994,10 +10722,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G126" s="5" t="n">
+        <v>-2.825076</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -11009,30 +10735,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J126" s="5" t="n">
-        <v>-1.417168</v>
-      </c>
-      <c r="K126" s="5" t="n">
-        <v>-0.856164</v>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Financing</t>
+        </is>
+      </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Loss before income taxes</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Net change in credit facilities</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
           <t>-</t>
@@ -11043,43 +10773,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G127" s="5" t="n">
+        <v>-0.013318</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I127" s="5" t="n">
-        <v>-11.956105</v>
-      </c>
-      <c r="J127" s="5" t="n">
-        <v>-9.343260000000001</v>
-      </c>
-      <c r="K127" s="5" t="n">
-        <v>-1.236051</v>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Income tax expense</t>
+          <t>Financing</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Deferred</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr"/>
+          <t>Repayment of long-term debt</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
@@ -11090,10 +10828,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G128" s="5" t="n">
+        <v>-0.275</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -11105,27 +10841,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J128" s="5" t="n">
-        <v>0.066792</v>
-      </c>
-      <c r="K128" s="5" t="n">
-        <v>0.141207</v>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Income tax expense</t>
+          <t>Investing</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Income tax expense total</t>
+          <t>Short-term investments</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
@@ -11144,44 +10884,42 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H129" s="5" t="n">
+        <v>-20.8</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J129" s="5" t="n">
-        <v>0.066792</v>
-      </c>
-      <c r="K129" s="5" t="n">
-        <v>0.141207</v>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Income tax expense</t>
+          <t>Investing</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Net loss</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Deposits on leases</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
@@ -11192,10 +10930,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G130" s="5" t="n">
+        <v>-0.0545</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -11207,27 +10943,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J130" s="5" t="n">
-        <v>-9.410052</v>
-      </c>
-      <c r="K130" s="5" t="n">
-        <v>-1.377258</v>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Item that may be reclassified subsequently to</t>
+          <t>Investing</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Foreign operations - foreign currency translation differences</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
@@ -11241,45 +10981,49 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G131" s="5" t="n">
+        <v>0.109453</v>
+      </c>
+      <c r="H131" s="5" t="n">
+        <v>0.398919</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J131" s="5" t="n">
-        <v>0.013567</v>
-      </c>
-      <c r="K131" s="5" t="n">
-        <v>0.020108</v>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Item that may be reclassified subsequently to</t>
+          <t>Investing</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Total comprehensive loss</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr"/>
+          <t>(Decrease) increase in cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
@@ -11290,49 +11034,45 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G132" s="5" t="n">
+        <v>36.53534</v>
+      </c>
+      <c r="H132" s="5" t="n">
+        <v>-41.462607</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J132" s="5" t="n">
-        <v>-9.396485</v>
-      </c>
-      <c r="K132" s="5" t="n">
-        <v>-1.35715</v>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Item that may be reclassified subsequently to</t>
+          <t>Standards Board ("IASB").</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share (note 18) $</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
@@ -11343,50 +11083,50 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G133" s="5" t="n">
+        <v>0.002023</v>
+      </c>
+      <c r="H133" s="5" t="n">
+        <v>2.5e-05</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J133" s="5" t="n">
-        <v>-3.1e-07</v>
-      </c>
-      <c r="K133" s="5" t="n">
-        <v>-5e-08</v>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Incorporation</t>
+        </is>
+      </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Restructuring expenses (note 17)</t>
+          <t>December 31, 2019 December</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E134" s="5" t="n">
+        <v>0.002018</v>
+      </c>
+      <c r="F134" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -11403,8 +11143,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J134" s="5" t="n">
-        <v>0.194252</v>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
@@ -11415,25 +11157,29 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Operating activities</t>
+        </is>
+      </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Net financial income (note 19)</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr"/>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss for the period $</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="n">
+        <v>-0.679725</v>
+      </c>
+      <c r="F135" s="5" t="n">
+        <v>-0.269157</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -11445,11 +11191,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I135" s="5" t="n">
-        <v>-1.757954</v>
-      </c>
-      <c r="J135" s="5" t="n">
-        <v>-1.417168</v>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
@@ -11460,24 +11210,26 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Income tax expense (recovery)</t>
+          <t>Item not affecting cash</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr"/>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Stock based compensation</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="n">
+        <v>0.1323</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11494,8 +11246,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I136" s="5" t="n">
-        <v>-0.035879</v>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
@@ -11511,29 +11265,29 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Income tax expense (recovery)</t>
+          <t>Net changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Deferred</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr"/>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="n">
+        <v>0.08121399999999999</v>
+      </c>
+      <c r="F137" s="5" t="n">
+        <v>0.004532</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -11545,11 +11299,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I137" s="5" t="n">
-        <v>0.042087</v>
-      </c>
-      <c r="J137" s="5" t="n">
-        <v>0.066792</v>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
@@ -11560,33 +11318,29 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Income tax expense (recovery)</t>
+          <t>Net changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Income tax expense (recovery) total</t>
+          <t>Net changes in non-cash working capital total</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="n">
+        <v>-0.466211</v>
+      </c>
+      <c r="F138" s="5" t="n">
+        <v>-0.264625</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -11598,11 +11352,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I138" s="5" t="n">
-        <v>0.006208</v>
-      </c>
-      <c r="J138" s="5" t="n">
-        <v>0.066792</v>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
@@ -11613,28 +11371,22 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Income tax expense (recovery)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Net loss</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net proceeds on issuance of common stock</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" s="5" t="n">
+        <v>0.821613</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11651,11 +11403,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I139" s="5" t="n">
-        <v>-11.962313</v>
-      </c>
-      <c r="J139" s="5" t="n">
-        <v>-9.410052</v>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
@@ -11666,29 +11422,29 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Other comprehensive income</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Foreign operations - foreign currency translation differences</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr"/>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net change in cash during the period $</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E140" s="5" t="n">
+        <v>0.355402</v>
+      </c>
+      <c r="F140" s="5" t="n">
+        <v>-0.264625</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -11700,11 +11456,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I140" s="5" t="n">
-        <v>0.051576</v>
-      </c>
-      <c r="J140" s="5" t="n">
-        <v>0.013567</v>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
@@ -11715,29 +11475,31 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Other comprehensive income</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Total comprehensive loss</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr"/>
+          <t>Cash, beginning of period</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F141" s="5" t="n">
+        <v>0.355402</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -11749,11 +11511,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I141" s="5" t="n">
-        <v>-11.910737</v>
-      </c>
-      <c r="J141" s="5" t="n">
-        <v>-9.396485</v>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
@@ -11764,33 +11530,29 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Other comprehensive income</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share (note 20) $</t>
+          <t>Cash, end of period $</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E142" s="5" t="n">
+        <v>0.355402</v>
+      </c>
+      <c r="F142" s="5" t="n">
+        <v>0.090777</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -11802,11 +11564,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I142" s="5" t="n">
-        <v>-3.8e-07</v>
-      </c>
-      <c r="J142" s="5" t="n">
-        <v>-3.1e-07</v>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
@@ -11817,21 +11583,33 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>incorporation) to December</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr"/>
-      <c r="E143" s="5" t="n">
-        <v>0.002018</v>
-      </c>
-      <c r="F143" s="5" t="n">
-        <v>3.1e-05</v>
+          <t>Cash, beginning of period $</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -11865,22 +11643,26 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Expenses relating to identification of qualifying</t>
-        </is>
-      </c>
+      <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Expenses relating to identification of qualifying transaction $</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr"/>
-      <c r="E144" s="5" t="n">
-        <v>0.43223</v>
-      </c>
-      <c r="F144" s="5" t="n">
-        <v>0.167285</v>
+          <t>Net revenue (note 15) $</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -11892,20 +11674,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I144" s="5" t="n">
+        <v>29.28832</v>
+      </c>
+      <c r="J144" s="5" t="n">
+        <v>30.242255</v>
+      </c>
+      <c r="K144" s="5" t="n">
+        <v>34.74792</v>
       </c>
     </row>
     <row r="145">
@@ -11914,49 +11690,41 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Expenses relating to identification of qualifying</t>
-        </is>
-      </c>
+      <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Stock based compensation (Note 8 (b))</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr"/>
-      <c r="E145" s="5" t="n">
-        <v>0.1323</v>
+          <t>Cost of goods sold</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>CostOfRevenue</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G145" s="5" t="n">
+        <v>12.307947</v>
+      </c>
+      <c r="H145" s="5" t="n">
+        <v>13.387834</v>
+      </c>
+      <c r="I145" s="5" t="n">
+        <v>13.853084</v>
+      </c>
+      <c r="J145" s="5" t="n">
+        <v>13.506585</v>
+      </c>
+      <c r="K145" s="5" t="n">
+        <v>12.268083</v>
       </c>
     </row>
     <row r="146">
@@ -11965,51 +11733,41 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Expenses relating to identification of qualifying</t>
-        </is>
-      </c>
+      <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Gross profit</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E146" s="5" t="n">
-        <v>0.032917</v>
-      </c>
-      <c r="F146" s="5" t="n">
-        <v>0.03645</v>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>GrossProfit</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G146" s="5" t="n">
+        <v>17.882972</v>
+      </c>
+      <c r="H146" s="5" t="n">
+        <v>15.693119</v>
+      </c>
+      <c r="I146" s="5" t="n">
+        <v>15.435236</v>
+      </c>
+      <c r="J146" s="5" t="n">
+        <v>16.73567</v>
+      </c>
+      <c r="K146" s="5" t="n">
+        <v>22.479837</v>
       </c>
     </row>
     <row r="147">
@@ -12018,14 +11776,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Expenses relating to identification of qualifying</t>
-        </is>
-      </c>
+      <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Office and administrative</t>
+          <t>Selling, general and administration expenses (note 16)</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -12033,11 +11787,15 @@
           <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
-      <c r="E147" s="5" t="n">
-        <v>0.082278</v>
-      </c>
-      <c r="F147" s="5" t="n">
-        <v>0.06542199999999999</v>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -12049,20 +11807,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I147" s="5" t="n">
+        <v>29.149295</v>
+      </c>
+      <c r="J147" s="5" t="n">
+        <v>27.301846</v>
+      </c>
+      <c r="K147" s="5" t="n">
+        <v>24.572052</v>
       </c>
     </row>
     <row r="148">
@@ -12071,22 +11823,22 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Expenses relating to identification of qualifying</t>
-        </is>
-      </c>
+      <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Expenses relating to identification of qualifying total</t>
+          <t>Restructuring expenses</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
-      <c r="E148" s="5" t="n">
-        <v>0.679725</v>
-      </c>
-      <c r="F148" s="5" t="n">
-        <v>0.269157</v>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -12103,10 +11855,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J148" s="5" t="n">
+        <v>0.194252</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
@@ -12120,26 +11870,22 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Expenses relating to identification of qualifying</t>
-        </is>
-      </c>
+      <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the period $</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E149" s="5" t="n">
-        <v>-0.679725</v>
-      </c>
-      <c r="F149" s="5" t="n">
-        <v>-0.269157</v>
+          <t>Net financial income (note 17)</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -12156,15 +11902,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J149" s="5" t="n">
+        <v>-1.417168</v>
+      </c>
+      <c r="K149" s="5" t="n">
+        <v>-0.856164</v>
       </c>
     </row>
     <row r="150">
@@ -12173,47 +11915,41 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Net loss per common share</t>
-        </is>
-      </c>
+      <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Basic and fully diluted (Note 9) $</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr"/>
-      <c r="E150" s="5" t="n">
-        <v>1.9e-07</v>
-      </c>
-      <c r="F150" s="5" t="n">
-        <v>8e-08</v>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Loss before income taxes</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G150" s="5" t="n">
+        <v>-10.075391</v>
+      </c>
+      <c r="H150" s="5" t="n">
+        <v>-17.54466</v>
+      </c>
+      <c r="I150" s="5" t="n">
+        <v>-11.956105</v>
+      </c>
+      <c r="J150" s="5" t="n">
+        <v>-9.343260000000001</v>
+      </c>
+      <c r="K150" s="5" t="n">
+        <v>-1.236051</v>
       </c>
     </row>
     <row r="151">
@@ -12224,20 +11960,24 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>outstanding</t>
+          <t>Income tax expense</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Basic and fully diluted (Note 9)</t>
+          <t>Deferred</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
-      <c r="E151" s="5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F151" s="5" t="n">
-        <v>3.5</v>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -12254,15 +11994,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J151" s="5" t="n">
+        <v>0.066792</v>
+      </c>
+      <c r="K151" s="5" t="n">
+        <v>0.141207</v>
       </c>
     </row>
     <row r="152">
@@ -12273,12 +12009,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Shares      Amount           surplus          Deficit                Total</t>
+          <t>Income tax expense</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Balance, January 15, 2018 - $ - $ - $</t>
+          <t>Income tax expense total</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
@@ -12307,15 +12043,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J152" s="5" t="n">
+        <v>0.066792</v>
+      </c>
+      <c r="K152" s="5" t="n">
+        <v>0.141207</v>
       </c>
     </row>
     <row r="153">
@@ -12326,17 +12058,23 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Shares issued for cash –</t>
+          <t>Income tax expense</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Shares issued for cash – founders' shares (Note 7) 11,200,000 560,000 -</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr"/>
-      <c r="E153" s="5" t="n">
-        <v>0.5600000000000001</v>
+          <t>Net loss</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12358,15 +12096,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J153" s="5" t="n">
+        <v>-9.410052</v>
+      </c>
+      <c r="K153" s="5" t="n">
+        <v>-1.377258</v>
       </c>
     </row>
     <row r="154">
@@ -12377,17 +12111,19 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Shares issued for cash –</t>
+          <t>Item that may be reclassified subsequently to</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Shares issued for cash – initial public offering (Note 7) 3,500,000 350,000 -</t>
+          <t>Foreign operations - foreign currency translation differences</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
-      <c r="E154" s="5" t="n">
-        <v>0.35</v>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12409,15 +12145,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J154" s="5" t="n">
+        <v>0.013567</v>
+      </c>
+      <c r="K154" s="5" t="n">
+        <v>0.020108</v>
       </c>
     </row>
     <row r="155">
@@ -12428,17 +12160,19 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Shares issued for cash –</t>
+          <t>Item that may be reclassified subsequently to</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Share issuance costs (Note 7) - (88,387) -</t>
+          <t>Total comprehensive loss</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
-      <c r="E155" s="5" t="n">
-        <v>-0.08838699999999999</v>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12460,15 +12194,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J155" s="5" t="n">
+        <v>-9.396485</v>
+      </c>
+      <c r="K155" s="5" t="n">
+        <v>-1.35715</v>
       </c>
     </row>
     <row r="156">
@@ -12479,17 +12209,23 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Stock options issued to</t>
+          <t>Item that may be reclassified subsequently to</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Stock options issued to directors (Note 8(b)) - - 132,300</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr"/>
-      <c r="E156" s="5" t="n">
-        <v>0.1323</v>
+          <t>Basic and diluted loss per share (note 18) $</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12511,15 +12247,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J156" s="5" t="n">
+        <v>-3.1e-07</v>
+      </c>
+      <c r="K156" s="5" t="n">
+        <v>-5e-08</v>
       </c>
     </row>
     <row r="157">
@@ -12528,14 +12260,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Stock options issued to agents</t>
-        </is>
-      </c>
+      <c r="B157" t="inlineStr"/>
       <c r="C157" t="inlineStr">
         <is>
-          <t>(Note 8 (a)) - (18,550) 18,550</t>
+          <t>Restructuring expenses (note 17)</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -12564,10 +12292,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J157" s="5" t="n">
+        <v>0.194252</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
@@ -12581,46 +12307,36 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Stock options issued to agents</t>
-        </is>
-      </c>
+      <c r="B158" t="inlineStr"/>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Net loss for the period - - -</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E158" s="5" t="n">
-        <v>-0.679725</v>
-      </c>
-      <c r="F158" s="5" t="n">
-        <v>-0.679725</v>
+          <t>Net financial income (note 19)</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H158" s="5" t="n">
+        <v>-0.877753</v>
+      </c>
+      <c r="I158" s="5" t="n">
+        <v>-1.757954</v>
+      </c>
+      <c r="J158" s="5" t="n">
+        <v>-1.417168</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
@@ -12636,20 +12352,24 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Stock options issued to agents</t>
+          <t>Income tax expense (recovery)</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2018 14,700,000 $ 803,063 $ 150,850 $</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
-      <c r="E159" s="5" t="n">
-        <v>0.274188</v>
-      </c>
-      <c r="F159" s="5" t="n">
-        <v>-0.679725</v>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
@@ -12661,10 +12381,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I159" s="5" t="n">
+        <v>-0.035879</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
@@ -12685,20 +12403,24 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Stock options issued to agents</t>
+          <t>Income tax expense (recovery)</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2019 14,700,000 $ 803,063 $ 150,850 $</t>
+          <t>Deferred</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
-      <c r="E160" s="5" t="n">
-        <v>0.005031</v>
-      </c>
-      <c r="F160" s="5" t="n">
-        <v>-0.948882</v>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
@@ -12710,15 +12432,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I160" s="5" t="n">
+        <v>0.042087</v>
+      </c>
+      <c r="J160" s="5" t="n">
+        <v>0.066792</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
@@ -12734,17 +12452,23 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Income tax expense (recovery)</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Expenses relating to identification of qualifying transaction $</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr"/>
-      <c r="E161" s="5" t="n">
-        <v>0.43223</v>
+          <t>Income tax expense (recovery) total</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12761,15 +12485,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I161" s="5" t="n">
+        <v>0.006208</v>
+      </c>
+      <c r="J161" s="5" t="n">
+        <v>0.066792</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
@@ -12785,17 +12505,23 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Income tax expense (recovery)</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Stock based compensation (Note 8 (b))</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
-      <c r="E162" s="5" t="n">
-        <v>0.1323</v>
+          <t>Net loss</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12812,15 +12538,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I162" s="5" t="n">
+        <v>-11.962313</v>
+      </c>
+      <c r="J162" s="5" t="n">
+        <v>-9.410052</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
@@ -12836,21 +12558,19 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other comprehensive income</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E163" s="5" t="n">
-        <v>0.032917</v>
+          <t>Foreign operations - foreign currency translation differences</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12867,15 +12587,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I163" s="5" t="n">
+        <v>0.051576</v>
+      </c>
+      <c r="J163" s="5" t="n">
+        <v>0.013567</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
@@ -12891,21 +12607,19 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other comprehensive income</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Office and administrative</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E164" s="5" t="n">
-        <v>0.082278</v>
+          <t>Total comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12922,15 +12636,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I164" s="5" t="n">
+        <v>-11.910737</v>
+      </c>
+      <c r="J164" s="5" t="n">
+        <v>-9.396485</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
@@ -12946,21 +12656,23 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other comprehensive income</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Expenses total</t>
+          <t>Basic and diluted loss per share (note 20) $</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E165" s="5" t="n">
-        <v>0.679725</v>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12977,15 +12689,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I165" s="5" t="n">
+        <v>-3.8e-07</v>
+      </c>
+      <c r="J165" s="5" t="n">
+        <v>-3.1e-07</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
@@ -12999,23 +12707,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the period</t>
+          <t>Net revenue (note 16) $</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E166" s="5" t="n">
-        <v>-0.679725</v>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13027,15 +12733,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H166" s="5" t="n">
+        <v>29.080953</v>
+      </c>
+      <c r="I166" s="5" t="n">
+        <v>29.28832</v>
       </c>
       <c r="J166" t="inlineStr">
         <is>
@@ -13054,46 +12756,2166 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr">
+      <c r="B167" t="inlineStr"/>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Selling, general and administration expenses (note 17)</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H167" s="5" t="n">
+        <v>34.115532</v>
+      </c>
+      <c r="I167" s="5" t="n">
+        <v>29.149295</v>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Income taxes (recovery) expense</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H168" s="5" t="n">
+        <v>-0.020974</v>
+      </c>
+      <c r="I168" s="5" t="n">
+        <v>-0.035879</v>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Income taxes (recovery) expense</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H169" s="5" t="n">
+        <v>0.041291</v>
+      </c>
+      <c r="I169" s="5" t="n">
+        <v>0.042087</v>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Income taxes (recovery) expense</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Income taxes (recovery) expense total</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H170" s="5" t="n">
+        <v>0.020317</v>
+      </c>
+      <c r="I170" s="5" t="n">
+        <v>0.006208</v>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Income taxes (recovery) expense</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Net loss</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H171" s="5" t="n">
+        <v>-17.564977</v>
+      </c>
+      <c r="I171" s="5" t="n">
+        <v>-11.962313</v>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Foreign operations - foreign currency translation</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Foreign operations - foreign currency translation differences</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G172" s="5" t="n">
+        <v>-0.153048</v>
+      </c>
+      <c r="H172" s="5" t="n">
+        <v>0.251656</v>
+      </c>
+      <c r="I172" s="5" t="n">
+        <v>0.051576</v>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Foreign operations - foreign currency translation</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Total comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G173" s="5" t="n">
+        <v>-9.997221</v>
+      </c>
+      <c r="H173" s="5" t="n">
+        <v>-17.313321</v>
+      </c>
+      <c r="I173" s="5" t="n">
+        <v>-11.910737</v>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Foreign operations - foreign currency translation</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per share (note 15) $</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H174" s="5" t="n">
+        <v>-5.4e-07</v>
+      </c>
+      <c r="I174" s="5" t="n">
+        <v>-3.8e-07</v>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Foreign operations - foreign currency translation</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G175" s="5" t="n">
+        <v>30.172972</v>
+      </c>
+      <c r="H175" s="5" t="n">
+        <v>32.336701</v>
+      </c>
+      <c r="I175" s="5" t="n">
+        <v>31.847391</v>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr"/>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Net revenue (note 17) $</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G176" s="5" t="n">
+        <v>30.190919</v>
+      </c>
+      <c r="H176" s="5" t="n">
+        <v>29.080953</v>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr"/>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Selling, general and administration expenses (note 18)</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G177" s="5" t="n">
+        <v>27.800985</v>
+      </c>
+      <c r="H177" s="5" t="n">
+        <v>34.115532</v>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr"/>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Net financial (income) expenses (note 20)</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G178" s="5" t="n">
+        <v>0.049062</v>
+      </c>
+      <c r="H178" s="5" t="n">
+        <v>-0.877753</v>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr"/>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Reverse acquisition of Mira X expenses</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G179" s="5" t="n">
+        <v>0.108316</v>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Income taxes expense (recovery)</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G180" s="5" t="n">
+        <v>-0.515049</v>
+      </c>
+      <c r="H180" s="5" t="n">
+        <v>-0.020974</v>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Income taxes expense (recovery)</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G181" s="5" t="n">
+        <v>0.283831</v>
+      </c>
+      <c r="H181" s="5" t="n">
+        <v>0.041291</v>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Income taxes expense (recovery)</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Income taxes expense (recovery) total</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G182" s="5" t="n">
+        <v>-0.231218</v>
+      </c>
+      <c r="H182" s="5" t="n">
+        <v>0.020317</v>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Income taxes expense (recovery)</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Net loss</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G183" s="5" t="n">
+        <v>-9.844173</v>
+      </c>
+      <c r="H183" s="5" t="n">
+        <v>-17.564977</v>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Foreign operations - foreign currency translation</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per share (note 16) $</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G184" s="5" t="n">
+        <v>-3.3e-07</v>
+      </c>
+      <c r="H184" s="5" t="n">
+        <v>-5.4e-07</v>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr"/>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>incorporation) to December</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" s="5" t="n">
+        <v>0.002018</v>
+      </c>
+      <c r="F185" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Expenses relating to identification of qualifying</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Expenses relating to identification of qualifying transaction $</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" s="5" t="n">
+        <v>0.43223</v>
+      </c>
+      <c r="F186" s="5" t="n">
+        <v>0.167285</v>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Expenses relating to identification of qualifying</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Stock based compensation (Note 8 (b))</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" s="5" t="n">
+        <v>0.1323</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Expenses relating to identification of qualifying</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E188" s="5" t="n">
+        <v>0.032917</v>
+      </c>
+      <c r="F188" s="5" t="n">
+        <v>0.03645</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Expenses relating to identification of qualifying</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Office and administrative</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E189" s="5" t="n">
+        <v>0.082278</v>
+      </c>
+      <c r="F189" s="5" t="n">
+        <v>0.06542199999999999</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Expenses relating to identification of qualifying</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Expenses relating to identification of qualifying total</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" s="5" t="n">
+        <v>0.679725</v>
+      </c>
+      <c r="F190" s="5" t="n">
+        <v>0.269157</v>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Expenses relating to identification of qualifying</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the period $</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E191" s="5" t="n">
+        <v>-0.679725</v>
+      </c>
+      <c r="F191" s="5" t="n">
+        <v>-0.269157</v>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Net loss per common share</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Basic and fully diluted (Note 9) $</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" s="5" t="n">
+        <v>1.9e-07</v>
+      </c>
+      <c r="F192" s="5" t="n">
+        <v>8e-08</v>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>outstanding</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Basic and fully diluted (Note 9)</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F193" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Shares      Amount           surplus          Deficit                Total</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Balance, January 15, 2018 - $ - $ - $</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Shares issued for cash –</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Shares issued for cash – founders' shares (Note 7) 11,200,000 560,000 -</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Shares issued for cash –</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Shares issued for cash – initial public offering (Note 7) 3,500,000 350,000 -</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Shares issued for cash –</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Share issuance costs (Note 7) - (88,387) -</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" s="5" t="n">
+        <v>-0.08838699999999999</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Stock options issued to</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Stock options issued to directors (Note 8(b)) - - 132,300</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" s="5" t="n">
+        <v>0.1323</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Stock options issued to agents</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>(Note 8 (a)) - (18,550) 18,550</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Stock options issued to agents</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Net loss for the period - - -</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E200" s="5" t="n">
+        <v>-0.679725</v>
+      </c>
+      <c r="F200" s="5" t="n">
+        <v>-0.679725</v>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Stock options issued to agents</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2018 14,700,000 $ 803,063 $ 150,850 $</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" s="5" t="n">
+        <v>0.274188</v>
+      </c>
+      <c r="F201" s="5" t="n">
+        <v>-0.679725</v>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Stock options issued to agents</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2019 14,700,000 $ 803,063 $ 150,850 $</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" s="5" t="n">
+        <v>0.005031</v>
+      </c>
+      <c r="F202" s="5" t="n">
+        <v>-0.948882</v>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Expenses relating to identification of qualifying transaction $</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" s="5" t="n">
+        <v>0.43223</v>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Stock based compensation (Note 8 (b))</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" s="5" t="n">
+        <v>0.1323</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E205" s="5" t="n">
+        <v>0.032917</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Office and administrative</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E206" s="5" t="n">
+        <v>0.082278</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Expenses total</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E207" s="5" t="n">
+        <v>0.679725</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the period</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E208" s="5" t="n">
+        <v>-0.679725</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
         <is>
           <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
+      <c r="C209" t="inlineStr">
         <is>
           <t>Basic and fully diluted (Note 9)</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
-      <c r="E167" s="5" t="n">
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" s="5" t="n">
         <v>3.5</v>
       </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr">
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
         <is>
           <t>-</t>
         </is>
